--- a/workshop/demos/tekla_data/nabidka.xlsx
+++ b/workshop/demos/tekla_data/nabidka.xlsx
@@ -438,7 +438,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cenová nabídka – ocelová konstrukce HALA SKLAD 24x48 (zakázka Z-2026-014, revize B)</t>
+          <t>Cenová nabídka – ocelová konstrukce Hala sklad Lipník 24 × 48 m (zakázka Z2026-021, revize B)</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
